--- a/assets/translations/Korean.RepublicOfKorea.ko-KO.xlsx
+++ b/assets/translations/Korean.RepublicOfKorea.ko-KO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44E49652-F0A2-E744-8DA7-515F137AF44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A390D1-0D8D-C34E-B211-BD96AB3CDF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="5240" windowWidth="32180" windowHeight="19420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11020" yWindow="3020" windowWidth="32180" windowHeight="19420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="221">
   <si>
     <t>Daylight has a wide range of energy across multiple wavelengths – it can be separated into all the colours of the rainbow.</t>
   </si>
@@ -287,91 +287,6 @@
   </si>
   <si>
     <t>빛은 뇌를 활성화시킨다. 아침의 빛은 신체 내부 시계를 앞당기고(더 이른 시간으로 맞추고), 저녁의 빛은 그것을 늦춘다(더 늦은 시간으로 맞춘다).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비시각적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>효과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (10 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">~ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>20)</t>
-    </r>
   </si>
   <si>
     <t>Light from the sun increases from dawn to midday and decreases in the evening. Depending on location, the amount of light in the day varies greatly between summer and winter.</t>
@@ -957,39 +872,66 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감광신경절 세포(</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>ipRGC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비시각적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빛을 신호로 변환하고, 그 신호는 많은 생리적 기능에 영향을 미친다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빛은 신체</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -999,18 +941,16 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>효과에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내부</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -1020,218 +960,41 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>연구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (24 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시계에 영향을 미치고, 그것은 수면-각성 패턴과 함께 다른 매일의 리듬을 조절한다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 26)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>생리적 반응에는 뚜렷한 개인차가 있다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감광신경절 세포(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ipRGC)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛을 신호로 변환하고, 그 신호는 많은 생리적 기능에 영향을 미친다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛은 신체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내부</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시계에 영향을 미치고, 그것은 수면-각성 패턴과 함께 다른 매일의 리듬을 조절한다.</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낮 시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 동안의 높은 빛 수준은 기분을 좋게 할 수 있다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">백색광은 </t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -1240,6 +1003,56 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
+      <t>우리가 색으로 지각하는 많은 파장으로 이루어져 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>실생활에서 빛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">에 노출되는 것에 대하여 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조사하는 연구가 필요하다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">저녁 때의 빛 노출은 우리 몸에게 아직 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
       <t>낮 시간</t>
     </r>
     <r>
@@ -1250,97 +1063,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 동안의 높은 빛 수준은 기분을 좋게 할 수 있다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비시각적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>효과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (10 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>임을 알려준다. 그것은 각성을 증가시키고 내부 시계를 더 늦은 시간으로 맞춘다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>빛 노출은 그것의 강도로 나타낼 수 있</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 20)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">백색광은 </t>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으며, 이는 관심 기능에 따라 가중치를 부여한 380 nm 에서 780 nm 까지의 모든 파장에서 나온 총 에너지량이다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">추상체는 망막에 있는 특수한 세포이다. 그 모양을 따서 이름을 붙인 것이다(현미경으로 보면 그렇게 보인다). 추상체가 가장 밀집한 곳은 </t>
     </r>
     <r>
       <rPr>
@@ -1350,170 +1093,47 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>우리가 색으로 지각하는 많은 파장으로 이루어져 있다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비시각적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>효과에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>영향을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>요인들</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (21 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>중심와(망막 중심에 있는)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">빛의 생리적 효과에 관한 대부분의 연구는 제한된 모집단(특정 연령집단, 민족, 건강 상태)에 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 23)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>실생활에서 빛</t>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>촛점을 맞추었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">. 앞으로의 연구는 더 넓은 지역과 다양한 모집단을 대상으로 이루어지는 것이 중요하다.   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>주광</t>
     </r>
     <r>
       <rPr>
@@ -1523,22 +1143,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">에 노출되는 것에 대하여 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>조사하는 연구가 필요하다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">저녁 때의 빛 노출은 우리 몸에게 아직 </t>
+      <t>(daylight)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">은 우리가 광대역 스펙트럼이라고 부르는 것을 가지며, 이는 </t>
     </r>
     <r>
       <rPr>
@@ -1548,22 +1163,25 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>낮 시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>임을 알려준다. 그것은 각성을 증가시키고 내부 시계를 더 늦은 시간으로 맞춘다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>빛 노출은 그것의 강도로 나타낼 수 있</t>
+      <t>넓은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 파장에 걸쳐 큰 에너지를 갖는다.</t>
+    </r>
+  </si>
+  <si>
+    <t>심화 정보</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">상이한 광원 기술은 다양한 소재를 이용하여 전기를 빛으로 변환한다. 상이한 소재로 인해 빛의 강도는 파장에 따라 다르게 </t>
     </r>
     <r>
       <rPr>
@@ -1573,12 +1191,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>으며, 이는 관심 기능에 따라 가중치를 부여한 380 nm 에서 780 nm 까지의 모든 파장에서 나온 총 에너지량이다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">추상체는 망막에 있는 특수한 세포이다. 그 모양을 따서 이름을 붙인 것이다(현미경으로 보면 그렇게 보인다). 추상체가 가장 밀집한 곳은 </t>
+      <t>분포한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">. 이러한 파장에 따른 빛의 </t>
     </r>
     <r>
       <rPr>
@@ -1588,22 +1211,22 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>중심와(망막 중심에 있는)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">빛의 생리적 효과에 관한 대부분의 연구는 제한된 모집단(특정 연령집단, 민족, 건강 상태)에 </t>
+      <t>분포를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 분광 분포라고 한다. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">상이한 전기 광원(예, LED 또는 </t>
     </r>
     <r>
       <rPr>
@@ -1613,176 +1236,96 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>촛점을 맞추었다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">. 앞으로의 연구는 더 넓은 지역과 다양한 모집단을 대상으로 이루어지는 것이 중요하다.   </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빛과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스펙트럼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>형광램프, 기타</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)은 서로 다른 스펙트럼을 가진다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>빛은 신체 내부 리듬을 조절</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 6)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">빛과 스펙트럼 (1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하도록 도와준다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>. 이는 생물학적 과정들이 적절한 시간에 시작하고 중단하도록 해준다.</t>
+    </r>
+  </si>
+  <si>
+    <t>단순화된 진술</t>
+  </si>
+  <si>
+    <t>과학적 진술</t>
+  </si>
+  <si>
+    <r>
+      <t>주광은 직사광</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 6)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인간의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>광수용기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (7 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(sunlight)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과 산란된 천공광</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 9)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>주광</t>
-    </r>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(skylight)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의 조합이며, 모든 가시 파장과 그 너머를 포함한다. 하루 중 시간대와 기상 조건의 변화는 파장 구성에서 변이를 가져온다. 그러한 변이는 눈에 보이는 주광의 색을 변화시킨다.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -1791,17 +1334,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>(daylight)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">은 우리가 광대역 스펙트럼이라고 부르는 것을 가지며, 이는 </t>
+      <t xml:space="preserve">우리는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">광원의 각 파장이 방출하는 </t>
     </r>
     <r>
       <rPr>
@@ -1811,25 +1354,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>넓은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 파장에 걸쳐 큰 에너지를 갖는다.</t>
-    </r>
-  </si>
-  <si>
-    <t>심화 정보</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">상이한 광원 기술은 다양한 소재를 이용하여 전기를 빛으로 변환한다. 상이한 소재로 인해 빛의 강도는 파장에 따라 다르게 </t>
+      <t>전력(power)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">을 표시함으로써 광원의 특성을 나타낼 수 있다. 이러한 </t>
     </r>
     <r>
       <rPr>
@@ -1839,17 +1374,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>분포한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">. 이러한 파장에 따른 빛의 </t>
+      <t>전력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을 강도</t>
     </r>
     <r>
       <rPr>
@@ -1859,22 +1394,17 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>분포를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 분광 분포라고 한다. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">상이한 전기 광원(예, LED 또는 </t>
+      <t>(intensity)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">라고 부른다. 물리학자들은 강도를 측정하는 반면, </t>
     </r>
     <r>
       <rPr>
@@ -1884,184 +1414,6 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>형광램프, 기타</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)은 서로 다른 스펙트럼을 가진다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>빛은 신체 내부 리듬을 조절</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하도록 도와준다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>. 이는 생물학적 과정들이 적절한 시간에 시작하고 중단하도록 해준다.</t>
-    </r>
-  </si>
-  <si>
-    <t>단순화된 진술</t>
-  </si>
-  <si>
-    <t>과학적 진술</t>
-  </si>
-  <si>
-    <r>
-      <t>주광은 직사광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(sunlight)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>과 산란된 천공광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(skylight)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의 조합이며, 모든 가시 파장과 그 너머를 포함한다. 하루 중 시간대와 기상 조건의 변화는 파장 구성에서 변이를 가져온다. 그러한 변이는 눈에 보이는 주광의 색을 변화시킨다.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">우리는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">광원의 각 파장이 방출하는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전력(power)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">을 표시함으로써 광원의 특성을 나타낼 수 있다. 이러한 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>을 강도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(intensity)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">라고 부른다. 물리학자들은 강도를 측정하는 반면, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
       <t>생리학자들</t>
     </r>
     <r>
@@ -2122,6 +1474,96 @@
   </si>
   <si>
     <t>빛 노출을 관리하는 것은 식단, 운동 및 수면 습관과 마찬가지로 건강한 생활양식의 일부이다.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">빛 과 스펙트럼 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(1 ~ 6)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">인간의 광수용기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(7 ~ 9)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">빛의 비시각적 효과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(10 ~ 20)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>빛의 비시각적 효과에 영향을 주는 요인들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (21 ~ 23)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">빛의 비시각적 효과에 관한 연구 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(24 ~ 26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">빛에 대한 생리적 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반응에는 뚜렷한 개인차가 있다.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2233,14 +1675,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <vertAlign val="superscript"/>
       <sz val="12"/>
       <color rgb="FF242424"/>
@@ -2265,6 +1699,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
@@ -2449,7 +1890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2493,9 +1934,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2521,11 +1959,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3050,102 +2488,102 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="F2" s="10" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A3" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>84</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A4" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A5" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3173,47 +2611,47 @@
     <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
     <col min="3" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="9" width="42.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.28515625" style="23" customWidth="1"/>
+    <col min="10" max="10" width="42.28515625" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>204</v>
+        <v>145</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>203</v>
+        <v>176</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>199</v>
+        <v>172</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="85">
       <c r="A2" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -3222,30 +2660,30 @@
         <v>1</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F2" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>188</v>
+        <v>42</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>184</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>56</v>
+        <v>132</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="68">
       <c r="A3" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C3" s="13">
         <v>2</v>
@@ -3254,30 +2692,30 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>89</v>
+        <v>123</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>88</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>66</v>
+        <v>47</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>65</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="114">
       <c r="A4" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C4" s="13">
         <v>3</v>
@@ -3286,30 +2724,30 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>192</v>
+        <v>90</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>187</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>103</v>
+        <v>149</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>206</v>
+        <v>34</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="95">
       <c r="A5" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -3320,28 +2758,28 @@
       <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>198</v>
+      <c r="F5" s="19" t="s">
+        <v>190</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="20" t="s">
-        <v>99</v>
+      <c r="H5" s="19" t="s">
+        <v>98</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>205</v>
+        <v>35</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="102">
       <c r="A6" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>196</v>
+        <v>180</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C6" s="6">
         <v>5</v>
@@ -3350,30 +2788,30 @@
         <v>5</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>201</v>
+        <v>147</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>193</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>116</v>
+        <v>170</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>200</v>
+        <v>48</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="58.5" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C7" s="6">
         <v>6</v>
@@ -3382,30 +2820,30 @@
         <v>6</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>113</v>
+        <v>129</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>138</v>
+        <v>58</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>111</v>
+        <v>118</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="70">
       <c r="A8" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>197</v>
+        <v>179</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="C8" s="6">
         <v>7</v>
@@ -3414,30 +2852,30 @@
         <v>7</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="20" t="s">
-        <v>137</v>
+      <c r="H8" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>151</v>
+        <v>49</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="76">
       <c r="A9" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>197</v>
+        <v>179</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="C9" s="6">
         <v>8</v>
@@ -3448,28 +2886,28 @@
       <c r="E9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>68</v>
+      <c r="F9" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>41</v>
+        <v>86</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>40</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>193</v>
+        <v>46</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="38">
       <c r="A10" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>197</v>
+        <v>179</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="C10" s="6">
         <v>9</v>
@@ -3478,30 +2916,30 @@
         <v>9</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>108</v>
+        <v>85</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>39</v>
+        <v>100</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>140</v>
+        <v>152</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="51">
       <c r="A11" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>31</v>
+        <v>160</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C11" s="6">
         <v>10</v>
@@ -3510,30 +2948,30 @@
         <v>10</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>184</v>
+        <v>127</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>181</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="20" t="s">
         <v>8</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>96</v>
+        <v>57</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="85">
       <c r="A12" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C12" s="6">
         <v>11</v>
@@ -3544,28 +2982,28 @@
       <c r="E12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>155</v>
+      <c r="F12" s="20" t="s">
+        <v>154</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>95</v>
+        <v>124</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>94</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="57">
       <c r="A13" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C13" s="6">
         <v>12</v>
@@ -3576,28 +3014,28 @@
       <c r="E13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>106</v>
+      <c r="F13" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="J13" s="24" t="s">
-        <v>202</v>
+      <c r="J13" s="23" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="57">
       <c r="A14" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C14" s="6">
         <v>13</v>
@@ -3606,30 +3044,30 @@
         <v>13</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>67</v>
+        <v>117</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="21" t="s">
-        <v>185</v>
+      <c r="H14" s="20" t="s">
+        <v>182</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="68">
       <c r="A15" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>31</v>
+        <v>160</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C15" s="6">
         <v>14</v>
@@ -3638,30 +3076,30 @@
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>160</v>
+        <v>91</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>159</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>70</v>
+        <v>60</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="J15" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="57">
       <c r="A16" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C16" s="6">
         <v>15</v>
@@ -3670,30 +3108,30 @@
         <v>15</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>64</v>
+        <v>43</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>158</v>
+        <v>109</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>97</v>
+        <v>119</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="68">
       <c r="A17" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C17" s="6">
         <v>16</v>
@@ -3702,30 +3140,30 @@
         <v>16</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>46</v>
+        <v>92</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>45</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="20" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>102</v>
+        <v>44</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="57">
       <c r="A18" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C18" s="6">
         <v>17</v>
@@ -3734,30 +3172,30 @@
         <v>17</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>139</v>
+        <v>108</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>138</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>159</v>
+        <v>114</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>158</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>191</v>
+        <v>121</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57">
       <c r="A19" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>31</v>
+        <v>160</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C19" s="6">
         <v>18</v>
@@ -3766,30 +3204,30 @@
         <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>186</v>
+        <v>113</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>183</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>178</v>
+        <v>106</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>177</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>172</v>
+        <v>126</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="51">
       <c r="A20" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>187</v>
+        <v>160</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C20" s="6">
         <v>19</v>
@@ -3800,28 +3238,28 @@
       <c r="E20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>100</v>
+        <v>122</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="68">
       <c r="A21" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>31</v>
+        <v>160</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C21" s="6">
         <v>20</v>
@@ -3830,30 +3268,30 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>73</v>
+        <v>168</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>72</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="24" t="s">
-        <v>98</v>
+      <c r="J21" s="23" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="57">
       <c r="A22" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>189</v>
+      <c r="B22" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="C22" s="6">
         <v>21</v>
@@ -3862,21 +3300,21 @@
         <v>21</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F22" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="19" t="s">
         <v>10</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J22" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="J22" s="23" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3884,8 +3322,8 @@
       <c r="A23" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>189</v>
+      <c r="B23" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="C23" s="6">
         <v>22</v>
@@ -3894,30 +3332,30 @@
         <v>22</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>65</v>
+        <v>53</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>136</v>
+        <v>128</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="24" t="s">
-        <v>112</v>
+      <c r="J23" s="23" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="51" customHeight="1">
       <c r="A24" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>189</v>
+      <c r="B24" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="C24" s="6">
         <v>23</v>
@@ -3926,30 +3364,30 @@
         <v>23</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>183</v>
+        <v>151</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>220</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>156</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="24" t="s">
-        <v>72</v>
+      <c r="J24" s="23" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="38">
       <c r="A25" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>182</v>
+        <v>70</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="C25" s="6">
         <v>24</v>
@@ -3958,30 +3396,30 @@
         <v>24</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>162</v>
+        <v>61</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>161</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>38</v>
+      <c r="H25" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>190</v>
+        <v>134</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="85">
       <c r="A26" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>182</v>
+        <v>70</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="C26" s="6">
         <v>25</v>
@@ -3990,30 +3428,30 @@
         <v>25</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>104</v>
+        <v>51</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>117</v>
+        <v>169</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="102">
+        <v>36</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="103" thickBot="1">
       <c r="A27" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>182</v>
+        <v>70</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="C27" s="8">
         <v>26</v>
@@ -4022,22 +3460,22 @@
         <v>26</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>156</v>
+        <v>87</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>74</v>
+        <v>153</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>51</v>
+        <v>32</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4058,58 +3496,58 @@
   <sheetData>
     <row r="1" spans="1:2" ht="23">
       <c r="A1" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="21">
-      <c r="A2" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>217</v>
+      <c r="A2" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="115" customHeight="1">
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>218</v>
+      <c r="B3" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="69">
       <c r="A4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="31" t="s">
-        <v>219</v>
+      <c r="B4" s="30" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="92">
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>220</v>
+      <c r="B5" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="92">
       <c r="A6" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>221</v>
+        <v>59</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="92">
       <c r="A7" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>222</v>
+        <v>56</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4123,33 +3561,33 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.42578125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="21" style="28" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="28" customWidth="1"/>
-    <col min="3" max="16384" width="9.42578125" style="28"/>
+    <col min="1" max="1" width="21" style="27" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="27" customWidth="1"/>
+    <col min="3" max="16384" width="9.42578125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>147</v>
+      <c r="A1" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>214</v>
+      <c r="A2" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>212</v>
+      <c r="A3" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/assets/translations/Korean.RepublicOfKorea.ko-KO.xlsx
+++ b/assets/translations/Korean.RepublicOfKorea.ko-KO.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11102"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apple\Desktop\박현수\HCL Lab\번역\Consensus\Revising\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F900B5DA-B0A2-7549-9015-AB97A5E47BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14145" activeTab="1"/>
+    <workbookView xWindow="1300" yWindow="620" windowWidth="28800" windowHeight="14140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="222">
   <si>
     <t>Daylight has a wide range of energy across multiple wavelengths – it can be separated into all the colours of the rainbow.</t>
   </si>
@@ -608,10 +609,6 @@
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
-    <t>합의문</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>빛에 대한 생리적 반응에는 뚜렷한 개인차가 있다.</t>
   </si>
   <si>
@@ -636,7 +633,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -652,7 +649,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -672,7 +669,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -683,7 +680,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -700,7 +697,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -711,7 +708,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -734,7 +731,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -745,7 +742,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -762,7 +759,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -772,7 +769,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -786,7 +783,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -797,7 +794,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -811,7 +808,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -822,7 +819,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -836,7 +833,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -847,7 +844,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -858,7 +855,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -869,7 +866,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -880,7 +877,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -891,7 +888,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -905,7 +902,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -915,7 +912,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -929,7 +926,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -939,7 +936,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -956,7 +953,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -967,7 +964,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -984,7 +981,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -995,7 +992,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -1042,7 +1039,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -1053,7 +1050,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -1066,8 +1063,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="24" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1076,7 +1073,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1167,7 +1164,7 @@
     <font>
       <sz val="15"/>
       <color theme="9"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1180,7 +1177,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1188,13 +1185,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1202,7 +1199,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1210,7 +1207,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1218,14 +1215,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1233,7 +1230,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1515,10 +1512,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Standard 2" xfId="2"/>
-    <cellStyle name="Standard 3" xfId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Standard 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
@@ -1699,7 +1696,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -1708,7 +1705,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2025,20 +2022,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="21.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="42.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="40.109375" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="10.6640625" style="3"/>
+    <col min="1" max="1" width="24.28515625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="21.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="42.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="40.140625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="10.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>127</v>
       </c>
@@ -2058,7 +2055,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="11" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
         <v>147</v>
       </c>
@@ -2078,7 +2075,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="11" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A3" s="11" t="s">
         <v>69</v>
       </c>
@@ -2098,7 +2095,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="11" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A4" s="11" t="s">
         <v>146</v>
       </c>
@@ -2118,7 +2115,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="11" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="11" customFormat="1" ht="18">
       <c r="A5" s="11" t="s">
         <v>146</v>
       </c>
@@ -2141,13 +2138,13 @@
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="F2" r:id="rId3" display="https://orcid.org/0000-0003-0951-780X"/>
-    <hyperlink ref="F3" r:id="rId4" display="https://orcid.org/0009-0007-7565-9714"/>
-    <hyperlink ref="D5" r:id="rId5"/>
-    <hyperlink ref="F4" r:id="rId6" display="https://orcid.org/0000-0003-4348-3690"/>
-    <hyperlink ref="F5" r:id="rId7" display="https://orcid.org/0009-0002-0079-1829"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F2" r:id="rId3" display="https://orcid.org/0000-0003-0951-780X" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F3" r:id="rId4" display="https://orcid.org/0009-0007-7565-9714" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F4" r:id="rId6" display="https://orcid.org/0000-0003-4348-3690" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F5" r:id="rId7" display="https://orcid.org/0009-0002-0079-1829" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2155,23 +2152,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="49.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="28" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="28" customWidth="1"/>
     <col min="3" max="4" width="10" style="1" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" style="28" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" style="28" customWidth="1"/>
-    <col min="9" max="9" width="42.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.33203125" style="35" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.28515625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="42.28515625" style="28" customWidth="1"/>
+    <col min="9" max="9" width="42.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.28515625" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="16" t="s">
         <v>61</v>
       </c>
@@ -2203,12 +2200,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="85">
       <c r="A2" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -2220,13 +2217,13 @@
         <v>113</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>115</v>
@@ -2235,12 +2232,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="68">
       <c r="A3" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C3" s="13">
         <v>2</v>
@@ -2267,12 +2264,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="103.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="102">
       <c r="A4" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C4" s="13">
         <v>3</v>
@@ -2296,15 +2293,15 @@
         <v>25</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="86.25" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="85">
       <c r="A5" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -2328,15 +2325,15 @@
         <v>26</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="90" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="102">
       <c r="A6" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="6">
         <v>5</v>
@@ -2360,15 +2357,15 @@
         <v>38</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="58.5" customHeight="1">
       <c r="A7" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" s="6">
         <v>6</v>
@@ -2395,12 +2392,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="87" customHeight="1">
       <c r="A8" s="17" t="s">
         <v>160</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C8" s="6">
         <v>7</v>
@@ -2421,18 +2418,18 @@
         <v>119</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="68">
       <c r="A9" s="17" t="s">
         <v>160</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="6">
         <v>8</v>
@@ -2459,12 +2456,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="34">
       <c r="A10" s="17" t="s">
         <v>160</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="6">
         <v>9</v>
@@ -2491,12 +2488,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="51">
       <c r="A11" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" s="6">
         <v>10</v>
@@ -2508,27 +2505,27 @@
         <v>110</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>131</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="85">
       <c r="A12" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C12" s="6">
         <v>11</v>
@@ -2540,7 +2537,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>107</v>
@@ -2552,15 +2549,15 @@
         <v>24</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="51">
       <c r="A13" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" s="6">
         <v>12</v>
@@ -2578,7 +2575,7 @@
         <v>49</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>1</v>
@@ -2587,12 +2584,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="51">
       <c r="A14" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C14" s="6">
         <v>13</v>
@@ -2610,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>32</v>
@@ -2619,12 +2616,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="68">
       <c r="A15" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C15" s="6">
         <v>14</v>
@@ -2651,12 +2648,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="51">
       <c r="A16" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="6">
         <v>15</v>
@@ -2683,12 +2680,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="68">
       <c r="A17" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="6">
         <v>16</v>
@@ -2700,27 +2697,27 @@
         <v>78</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>40</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="51">
       <c r="A18" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" s="6">
         <v>17</v>
@@ -2747,12 +2744,12 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="51">
       <c r="A19" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" s="6">
         <v>18</v>
@@ -2779,12 +2776,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="51">
       <c r="A20" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C20" s="6">
         <v>19</v>
@@ -2802,7 +2799,7 @@
         <v>116</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>105</v>
@@ -2811,12 +2808,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="68">
       <c r="A21" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" s="6">
         <v>20</v>
@@ -2828,7 +2825,7 @@
         <v>79</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>149</v>
@@ -2843,12 +2840,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="51">
       <c r="A22" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C22" s="6">
         <v>21</v>
@@ -2875,12 +2872,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="51.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="51">
       <c r="A23" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C23" s="6">
         <v>22</v>
@@ -2907,12 +2904,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="51" customHeight="1">
       <c r="A24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" s="6">
         <v>23</v>
@@ -2924,7 +2921,7 @@
         <v>134</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>88</v>
@@ -2939,12 +2936,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="34">
       <c r="A25" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="6">
         <v>24</v>
@@ -2956,7 +2953,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>18</v>
@@ -2971,12 +2968,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="85">
       <c r="A26" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="6">
         <v>25</v>
@@ -3003,12 +3000,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="91.5" customHeight="1" thickBot="1">
       <c r="A27" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="8">
         <v>26</v>
@@ -3029,10 +3026,10 @@
         <v>60</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J27" s="34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3043,16 +3040,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="23">
       <c r="A1" s="15" t="s">
         <v>67</v>
       </c>
@@ -3060,7 +3057,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" ht="21">
       <c r="A2" s="20" t="s">
         <v>173</v>
       </c>
@@ -3068,7 +3065,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="114.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" ht="115" customHeight="1">
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
@@ -3076,7 +3073,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="69">
       <c r="A4" s="15" t="s">
         <v>21</v>
       </c>
@@ -3084,7 +3081,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="96" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="92">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
@@ -3092,7 +3089,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="96" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="92">
       <c r="A6" s="15" t="s">
         <v>46</v>
       </c>
@@ -3100,7 +3097,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="96" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" ht="92">
       <c r="A7" s="15" t="s">
         <v>43</v>
       </c>
@@ -3116,16 +3113,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.42578125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21" style="19" customWidth="1"/>
-    <col min="2" max="2" width="28.44140625" style="19" customWidth="1"/>
-    <col min="3" max="16384" width="9.44140625" style="19"/>
+    <col min="2" max="2" width="28.42578125" style="19" customWidth="1"/>
+    <col min="3" max="16384" width="9.42578125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
         <v>67</v>
       </c>
@@ -3133,18 +3130,16 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="19" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" s="36"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="19" t="s">
         <v>171</v>
       </c>
